--- a/documentation/stm32_wifi_pinout.xlsx
+++ b/documentation/stm32_wifi_pinout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISI\Documents\Alvaro\Window_Control\Window_Control\STM32_wifi\STM32Workspace\ST67W6X_HTTP_Server\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISI\Documents\Alvaro\Window_Control\Window_Control\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8CDF41-CAD3-4585-B111-295EF2E6703F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BBBF70-F536-44C0-8C72-5A9C9B671AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11955" yWindow="1710" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pinout" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="209">
   <si>
     <t>Tag</t>
   </si>
@@ -373,24 +373,6 @@
     <t>EXTI15, rising/falling edge</t>
   </si>
   <si>
-    <t>USER_BUTTON</t>
-  </si>
-  <si>
-    <t>User button interrupt input</t>
-  </si>
-  <si>
-    <t>03 EXTI - User</t>
-  </si>
-  <si>
-    <t>PF12</t>
-  </si>
-  <si>
-    <t>GPIO_EXTI12</t>
-  </si>
-  <si>
-    <t>EXTI12, falling edge</t>
-  </si>
-  <si>
     <t>Vertical_ENABLE</t>
   </si>
   <si>
@@ -572,6 +554,99 @@
   </si>
   <si>
     <t>PE11</t>
+  </si>
+  <si>
+    <t>GPS_enable</t>
+  </si>
+  <si>
+    <t>Enable power switch to power GPS</t>
+  </si>
+  <si>
+    <t>06 GPIO - GPS</t>
+  </si>
+  <si>
+    <t>PG12</t>
+  </si>
+  <si>
+    <t>YLYB</t>
+  </si>
+  <si>
+    <t>YLEB</t>
+  </si>
+  <si>
+    <t>YREB</t>
+  </si>
+  <si>
+    <t>YRIB</t>
+  </si>
+  <si>
+    <t>ZLI</t>
+  </si>
+  <si>
+    <t>ZRI</t>
+  </si>
+  <si>
+    <t>ZL Internal limit switch input</t>
+  </si>
+  <si>
+    <t>ZR Internal limit switch input</t>
+  </si>
+  <si>
+    <t>YLY Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>YLE Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>YRE Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>YRI Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI8</t>
+  </si>
+  <si>
+    <t>PB8</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI7</t>
+  </si>
+  <si>
+    <t>PE6</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI6</t>
+  </si>
+  <si>
+    <t>PG0</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI0</t>
+  </si>
+  <si>
+    <t>PG9</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI9</t>
+  </si>
+  <si>
+    <t>PG10</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI10</t>
+  </si>
+  <si>
+    <t>USER_BUTTOM</t>
+  </si>
+  <si>
+    <t>PC13</t>
+  </si>
+  <si>
+    <t>Runs automode in migration ONLY</t>
+  </si>
+  <si>
+    <t>MIGRATION TEST ONLY</t>
   </si>
 </sst>
 </file>
@@ -946,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1558,176 +1633,173 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>190</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>197</v>
       </c>
       <c r="E31" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="F31" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>199</v>
       </c>
       <c r="E32" t="s">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="F32" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D34" t="s">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="E34" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="E36" t="s">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>205</v>
       </c>
       <c r="B37" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>206</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="B38" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E38" t="s">
         <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="B39" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s">
         <v>79</v>
@@ -1738,16 +1810,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D40" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="E40" t="s">
         <v>79</v>
@@ -1758,36 +1830,36 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="B41" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="E41" t="s">
         <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="B42" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="C42" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D42" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="E42" t="s">
         <v>79</v>
@@ -1798,16 +1870,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="E43" t="s">
         <v>79</v>
@@ -1818,16 +1890,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="B44" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="E44" t="s">
         <v>79</v>
@@ -1838,16 +1910,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="B45" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="C45" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="E45" t="s">
         <v>79</v>
@@ -1858,16 +1930,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="B46" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C46" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D46" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="E46" t="s">
         <v>79</v>
@@ -1878,36 +1950,36 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B47" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="C47" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D47" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="E47" t="s">
         <v>79</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="B48" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D48" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="E48" t="s">
         <v>79</v>
@@ -1918,16 +1990,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="B49" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="C49" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D49" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="E49" t="s">
         <v>79</v>
@@ -1938,16 +2010,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="B50" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="E50" t="s">
         <v>79</v>
@@ -1956,8 +2028,145 @@
         <v>10</v>
       </c>
     </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>159</v>
+      </c>
+      <c r="B51" t="s">
+        <v>160</v>
+      </c>
+      <c r="C51" t="s">
+        <v>148</v>
+      </c>
+      <c r="D51" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" t="s">
+        <v>164</v>
+      </c>
+      <c r="D52" t="s">
+        <v>165</v>
+      </c>
+      <c r="E52" t="s">
+        <v>79</v>
+      </c>
+      <c r="F52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" t="s">
+        <v>79</v>
+      </c>
+      <c r="F53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>169</v>
+      </c>
+      <c r="B54" t="s">
+        <v>170</v>
+      </c>
+      <c r="C54" t="s">
+        <v>164</v>
+      </c>
+      <c r="D54" t="s">
+        <v>171</v>
+      </c>
+      <c r="E54" t="s">
+        <v>79</v>
+      </c>
+      <c r="F54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>172</v>
+      </c>
+      <c r="B55" t="s">
+        <v>173</v>
+      </c>
+      <c r="C55" t="s">
+        <v>164</v>
+      </c>
+      <c r="D55" t="s">
+        <v>174</v>
+      </c>
+      <c r="E55" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>175</v>
+      </c>
+      <c r="B56" t="s">
+        <v>176</v>
+      </c>
+      <c r="C56" t="s">
+        <v>164</v>
+      </c>
+      <c r="D56" t="s">
+        <v>177</v>
+      </c>
+      <c r="E56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>178</v>
+      </c>
+      <c r="B57" t="s">
+        <v>179</v>
+      </c>
+      <c r="C57" t="s">
+        <v>180</v>
+      </c>
+      <c r="D57" t="s">
+        <v>181</v>
+      </c>
+      <c r="E57" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F50" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F56" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/documentation/stm32_wifi_pinout.xlsx
+++ b/documentation/stm32_wifi_pinout.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISI\Documents\Alvaro\Window_Control\Window_Control\STM32_wifi\STM32Workspace\ST67W6X_HTTP_Server\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISI\Documents\Alvaro\Window_Control\Window_Control\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8CDF41-CAD3-4585-B111-295EF2E6703F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1284F87F-CD23-4D87-9838-E0DD1EF0AA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="1710" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pinout" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="209">
   <si>
     <t>Tag</t>
   </si>
@@ -373,24 +373,6 @@
     <t>EXTI15, rising/falling edge</t>
   </si>
   <si>
-    <t>USER_BUTTON</t>
-  </si>
-  <si>
-    <t>User button interrupt input</t>
-  </si>
-  <si>
-    <t>03 EXTI - User</t>
-  </si>
-  <si>
-    <t>PF12</t>
-  </si>
-  <si>
-    <t>GPIO_EXTI12</t>
-  </si>
-  <si>
-    <t>EXTI12, falling edge</t>
-  </si>
-  <si>
     <t>Vertical_ENABLE</t>
   </si>
   <si>
@@ -572,6 +554,99 @@
   </si>
   <si>
     <t>PE11</t>
+  </si>
+  <si>
+    <t>GPS_enable</t>
+  </si>
+  <si>
+    <t>Enable power switch to power GPS</t>
+  </si>
+  <si>
+    <t>06 GPIO - GPS</t>
+  </si>
+  <si>
+    <t>PG12</t>
+  </si>
+  <si>
+    <t>YLYB</t>
+  </si>
+  <si>
+    <t>YLEB</t>
+  </si>
+  <si>
+    <t>YREB</t>
+  </si>
+  <si>
+    <t>YRIB</t>
+  </si>
+  <si>
+    <t>ZLI</t>
+  </si>
+  <si>
+    <t>ZRI</t>
+  </si>
+  <si>
+    <t>ZL Internal limit switch input</t>
+  </si>
+  <si>
+    <t>ZR Internal limit switch input</t>
+  </si>
+  <si>
+    <t>YLY Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>YLE Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>YRE Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>YRI Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI8</t>
+  </si>
+  <si>
+    <t>PB8</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI7</t>
+  </si>
+  <si>
+    <t>PE6</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI6</t>
+  </si>
+  <si>
+    <t>PG0</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI0</t>
+  </si>
+  <si>
+    <t>PG9</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI9</t>
+  </si>
+  <si>
+    <t>PG10</t>
+  </si>
+  <si>
+    <t>GPIO_EXTI10</t>
+  </si>
+  <si>
+    <t>USER_BUTTOM</t>
+  </si>
+  <si>
+    <t>PC13</t>
+  </si>
+  <si>
+    <t>Runs automode in migration ONLY</t>
+  </si>
+  <si>
+    <t>MIGRATION TEST ONLY</t>
   </si>
 </sst>
 </file>
@@ -946,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1558,176 +1633,173 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>117</v>
+        <v>182</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>190</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>197</v>
       </c>
       <c r="E31" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="F31" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>123</v>
+        <v>183</v>
       </c>
       <c r="B32" t="s">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>126</v>
+        <v>199</v>
       </c>
       <c r="E32" t="s">
-        <v>79</v>
+        <v>200</v>
       </c>
       <c r="F32" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="E33" t="s">
-        <v>79</v>
+        <v>202</v>
       </c>
       <c r="F33" t="s">
-        <v>10</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D34" t="s">
-        <v>133</v>
+        <v>203</v>
       </c>
       <c r="E34" t="s">
-        <v>79</v>
+        <v>204</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
+        <v>188</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>136</v>
+        <v>74</v>
       </c>
       <c r="E35" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s">
-        <v>138</v>
+        <v>189</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="E36" t="s">
-        <v>79</v>
+        <v>194</v>
       </c>
       <c r="F36" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>140</v>
+        <v>205</v>
       </c>
       <c r="B37" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="D37" t="s">
-        <v>142</v>
+        <v>206</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
-      </c>
-      <c r="F37" t="s">
-        <v>10</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="B38" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E38" t="s">
         <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="B39" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D39" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s">
         <v>79</v>
@@ -1738,16 +1810,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="B40" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D40" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="E40" t="s">
         <v>79</v>
@@ -1758,36 +1830,36 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="B41" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="E41" t="s">
         <v>79</v>
       </c>
       <c r="F41" t="s">
-        <v>127</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="B42" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="C42" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D42" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="E42" t="s">
         <v>79</v>
@@ -1798,16 +1870,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="B43" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C43" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D43" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="E43" t="s">
         <v>79</v>
@@ -1818,16 +1890,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="B44" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="C44" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D44" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="E44" t="s">
         <v>79</v>
@@ -1838,16 +1910,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="B45" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="C45" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="D45" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="E45" t="s">
         <v>79</v>
@@ -1858,16 +1930,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="B46" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C46" t="s">
-        <v>170</v>
+        <v>119</v>
       </c>
       <c r="D46" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
       <c r="E46" t="s">
         <v>79</v>
@@ -1878,36 +1950,36 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="B47" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="C47" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D47" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="E47" t="s">
         <v>79</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>121</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="B48" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D48" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="E48" t="s">
         <v>79</v>
@@ -1918,16 +1990,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="B49" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="C49" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D49" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="E49" t="s">
         <v>79</v>
@@ -1938,16 +2010,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="B50" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
       <c r="D50" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="E50" t="s">
         <v>79</v>
@@ -1956,8 +2028,145 @@
         <v>10</v>
       </c>
     </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>159</v>
+      </c>
+      <c r="B51" t="s">
+        <v>160</v>
+      </c>
+      <c r="C51" t="s">
+        <v>148</v>
+      </c>
+      <c r="D51" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51" t="s">
+        <v>79</v>
+      </c>
+      <c r="F51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" t="s">
+        <v>164</v>
+      </c>
+      <c r="D52" t="s">
+        <v>165</v>
+      </c>
+      <c r="E52" t="s">
+        <v>79</v>
+      </c>
+      <c r="F52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>166</v>
+      </c>
+      <c r="B53" t="s">
+        <v>167</v>
+      </c>
+      <c r="C53" t="s">
+        <v>164</v>
+      </c>
+      <c r="D53" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" t="s">
+        <v>79</v>
+      </c>
+      <c r="F53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>169</v>
+      </c>
+      <c r="B54" t="s">
+        <v>170</v>
+      </c>
+      <c r="C54" t="s">
+        <v>164</v>
+      </c>
+      <c r="D54" t="s">
+        <v>171</v>
+      </c>
+      <c r="E54" t="s">
+        <v>79</v>
+      </c>
+      <c r="F54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>172</v>
+      </c>
+      <c r="B55" t="s">
+        <v>173</v>
+      </c>
+      <c r="C55" t="s">
+        <v>164</v>
+      </c>
+      <c r="D55" t="s">
+        <v>174</v>
+      </c>
+      <c r="E55" t="s">
+        <v>79</v>
+      </c>
+      <c r="F55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>175</v>
+      </c>
+      <c r="B56" t="s">
+        <v>176</v>
+      </c>
+      <c r="C56" t="s">
+        <v>164</v>
+      </c>
+      <c r="D56" t="s">
+        <v>177</v>
+      </c>
+      <c r="E56" t="s">
+        <v>79</v>
+      </c>
+      <c r="F56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>178</v>
+      </c>
+      <c r="B57" t="s">
+        <v>179</v>
+      </c>
+      <c r="C57" t="s">
+        <v>180</v>
+      </c>
+      <c r="D57" t="s">
+        <v>181</v>
+      </c>
+      <c r="E57" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F50" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F56" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/documentation/stm32_wifi_pinout.xlsx
+++ b/documentation/stm32_wifi_pinout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISI\Documents\Alvaro\Window_Control\Window_Control\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3BBBF70-F536-44C0-8C72-5A9C9B671AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43568149-5A03-4AEF-A39E-327FB3DE3C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11955" yWindow="1710" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18690" yWindow="1710" windowWidth="10110" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pinout" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="215">
   <si>
     <t>Tag</t>
   </si>
@@ -647,6 +647,24 @@
   </si>
   <si>
     <t>MIGRATION TEST ONLY</t>
+  </si>
+  <si>
+    <t>EXTI6, rising/falling edge</t>
+  </si>
+  <si>
+    <t>EXTI0, rising/falling edge</t>
+  </si>
+  <si>
+    <t>EXTI7, rising/falling edge</t>
+  </si>
+  <si>
+    <t>EXTI8, rising/falling edge</t>
+  </si>
+  <si>
+    <t>EXTI10, rising/falling edge</t>
+  </si>
+  <si>
+    <t>EXTI9, rising/falling edge</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1666,7 @@
         <v>198</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1668,7 +1686,7 @@
         <v>200</v>
       </c>
       <c r="F32" t="s">
-        <v>96</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1688,7 +1706,7 @@
         <v>202</v>
       </c>
       <c r="F33" t="s">
-        <v>101</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1708,7 +1726,7 @@
         <v>204</v>
       </c>
       <c r="F34" t="s">
-        <v>106</v>
+        <v>213</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1728,7 +1746,7 @@
         <v>196</v>
       </c>
       <c r="F35" t="s">
-        <v>111</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1748,7 +1766,7 @@
         <v>194</v>
       </c>
       <c r="F36" t="s">
-        <v>116</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">

--- a/documentation/stm32_wifi_pinout.xlsx
+++ b/documentation/stm32_wifi_pinout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISI\Documents\Alvaro\Window_Control\Window_Control\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1284F87F-CD23-4D87-9838-E0DD1EF0AA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324D5603-31BC-4ABF-9E92-A4A05694BA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="1710" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27105" yWindow="75" windowWidth="25335" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pinout" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="216">
   <si>
     <t>Tag</t>
   </si>
@@ -647,6 +647,27 @@
   </si>
   <si>
     <t>MIGRATION TEST ONLY</t>
+  </si>
+  <si>
+    <t>EXTI6, rising/falling edge</t>
+  </si>
+  <si>
+    <t>EXTI0, rising/falling edge</t>
+  </si>
+  <si>
+    <t>EXTI9, rising/falling edge; physical pin also has NJTRST alternate debug name</t>
+  </si>
+  <si>
+    <t>EXTI10, rising/falling edge</t>
+  </si>
+  <si>
+    <t>EXTI7, rising/falling edge</t>
+  </si>
+  <si>
+    <t>EXTI8, rising/falling edge</t>
+  </si>
+  <si>
+    <t>PE7</t>
   </si>
 </sst>
 </file>
@@ -1648,7 +1669,7 @@
         <v>198</v>
       </c>
       <c r="F31" t="s">
-        <v>91</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1668,7 +1689,7 @@
         <v>200</v>
       </c>
       <c r="F32" t="s">
-        <v>96</v>
+        <v>210</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1688,7 +1709,7 @@
         <v>202</v>
       </c>
       <c r="F33" t="s">
-        <v>101</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1708,7 +1729,7 @@
         <v>204</v>
       </c>
       <c r="F34" t="s">
-        <v>106</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1722,13 +1743,13 @@
         <v>88</v>
       </c>
       <c r="D35" t="s">
-        <v>74</v>
+        <v>215</v>
       </c>
       <c r="E35" t="s">
         <v>196</v>
       </c>
       <c r="F35" t="s">
-        <v>111</v>
+        <v>213</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1748,7 +1769,7 @@
         <v>194</v>
       </c>
       <c r="F36" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">

--- a/documentation/stm32_wifi_pinout.xlsx
+++ b/documentation/stm32_wifi_pinout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISI\Documents\Alvaro\Window_Control\Window_Control\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324D5603-31BC-4ABF-9E92-A4A05694BA8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CA8F09-2E41-49F3-BDEF-4876F5912779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27105" yWindow="75" windowWidth="25335" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pinout" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="216">
   <si>
     <t>Tag</t>
   </si>
@@ -280,12 +280,6 @@
     <t>EXTI13, rising/falling edge</t>
   </si>
   <si>
-    <t>YLY</t>
-  </si>
-  <si>
-    <t>YLY limit switch input</t>
-  </si>
-  <si>
     <t>03 EXTI - Limit switches</t>
   </si>
   <si>
@@ -298,12 +292,6 @@
     <t>EXTI1, rising/falling edge</t>
   </si>
   <si>
-    <t>YLE</t>
-  </si>
-  <si>
-    <t>YLE limit switch input</t>
-  </si>
-  <si>
     <t>PB2</t>
   </si>
   <si>
@@ -313,12 +301,6 @@
     <t>EXTI2, rising/falling edge</t>
   </si>
   <si>
-    <t>YRE</t>
-  </si>
-  <si>
-    <t>YRE limit switch input</t>
-  </si>
-  <si>
     <t>PB4 (NJTRST)</t>
   </si>
   <si>
@@ -328,9 +310,6 @@
     <t>EXTI4, rising/falling edge; physical pin also has NJTRST alternate debug name</t>
   </si>
   <si>
-    <t>YRI</t>
-  </si>
-  <si>
     <t>YRI limit switch input</t>
   </si>
   <si>
@@ -568,18 +547,6 @@
     <t>PG12</t>
   </si>
   <si>
-    <t>YLYB</t>
-  </si>
-  <si>
-    <t>YLEB</t>
-  </si>
-  <si>
-    <t>YREB</t>
-  </si>
-  <si>
-    <t>YRIB</t>
-  </si>
-  <si>
     <t>ZLI</t>
   </si>
   <si>
@@ -592,18 +559,6 @@
     <t>ZR Internal limit switch input</t>
   </si>
   <si>
-    <t>YLY Bottom limit switch input</t>
-  </si>
-  <si>
-    <t>YLE Bottom limit switch input</t>
-  </si>
-  <si>
-    <t>YRE Bottom limit switch input</t>
-  </si>
-  <si>
-    <t>YRI Bottom limit switch input</t>
-  </si>
-  <si>
     <t>GPIO_EXTI8</t>
   </si>
   <si>
@@ -668,6 +623,51 @@
   </si>
   <si>
     <t>PE7</t>
+  </si>
+  <si>
+    <t>XLI Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>XLIB</t>
+  </si>
+  <si>
+    <t>XLEB</t>
+  </si>
+  <si>
+    <t>XLE Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>XREB</t>
+  </si>
+  <si>
+    <t>XRE Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>XRIB</t>
+  </si>
+  <si>
+    <t>XRI Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>XLI</t>
+  </si>
+  <si>
+    <t>XLI limit switch input</t>
+  </si>
+  <si>
+    <t>XLE</t>
+  </si>
+  <si>
+    <t>XLE limit switch input</t>
+  </si>
+  <si>
+    <t>XRE</t>
+  </si>
+  <si>
+    <t>XRE limit switch input</t>
+  </si>
+  <si>
+    <t>XRI</t>
   </si>
 </sst>
 </file>
@@ -1534,256 +1534,256 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" t="s">
         <v>86</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>88</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>89</v>
-      </c>
-      <c r="E25" t="s">
-        <v>90</v>
-      </c>
-      <c r="F25" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>211</v>
+      </c>
+      <c r="B26" t="s">
+        <v>212</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" t="s">
         <v>92</v>
-      </c>
-      <c r="B26" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>213</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E28" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>202</v>
+      </c>
+      <c r="B31" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" t="s">
         <v>182</v>
       </c>
-      <c r="B31" t="s">
-        <v>190</v>
-      </c>
-      <c r="C31" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" t="s">
-        <v>197</v>
-      </c>
       <c r="E31" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="F31" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="E32" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="F32" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B33" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="E33" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F33" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F34" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E35" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="F35" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B36" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="F36" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="D37" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E37" t="s">
         <v>84</v>
@@ -1791,36 +1791,36 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E38" t="s">
         <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E39" t="s">
         <v>79</v>
@@ -1831,16 +1831,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E40" t="s">
         <v>79</v>
@@ -1851,16 +1851,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B41" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E41" t="s">
         <v>79</v>
@@ -1871,16 +1871,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C42" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E42" t="s">
         <v>79</v>
@@ -1891,16 +1891,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E43" t="s">
         <v>79</v>
@@ -1911,16 +1911,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E44" t="s">
         <v>79</v>
@@ -1931,16 +1931,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D45" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E45" t="s">
         <v>79</v>
@@ -1951,16 +1951,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E46" t="s">
         <v>79</v>
@@ -1971,36 +1971,36 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D47" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
         <v>79</v>
       </c>
       <c r="F47" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B48" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
         <v>79</v>
@@ -2011,16 +2011,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C49" t="s">
+        <v>141</v>
+      </c>
+      <c r="D49" t="s">
         <v>148</v>
-      </c>
-      <c r="D49" t="s">
-        <v>155</v>
       </c>
       <c r="E49" t="s">
         <v>79</v>
@@ -2031,16 +2031,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B50" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C50" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D50" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E50" t="s">
         <v>79</v>
@@ -2051,16 +2051,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C51" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D51" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E51" t="s">
         <v>79</v>
@@ -2071,16 +2071,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B52" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D52" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E52" t="s">
         <v>79</v>
@@ -2091,16 +2091,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B53" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D53" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E53" t="s">
         <v>79</v>
@@ -2111,16 +2111,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B54" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D54" t="s">
         <v>164</v>
-      </c>
-      <c r="D54" t="s">
-        <v>171</v>
       </c>
       <c r="E54" t="s">
         <v>79</v>
@@ -2131,16 +2131,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B55" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D55" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E55" t="s">
         <v>79</v>
@@ -2151,16 +2151,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B56" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C56" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D56" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E56" t="s">
         <v>79</v>
@@ -2171,16 +2171,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B57" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E57" t="s">
         <v>79</v>

--- a/documentation/stm32_wifi_pinout.xlsx
+++ b/documentation/stm32_wifi_pinout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ISI\Documents\Alvaro\Window_Control\Window_Control\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43568149-5A03-4AEF-A39E-327FB3DE3C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67CA8F09-2E41-49F3-BDEF-4876F5912779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18690" yWindow="1710" windowWidth="10110" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pinout" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="216">
   <si>
     <t>Tag</t>
   </si>
@@ -280,12 +280,6 @@
     <t>EXTI13, rising/falling edge</t>
   </si>
   <si>
-    <t>YLY</t>
-  </si>
-  <si>
-    <t>YLY limit switch input</t>
-  </si>
-  <si>
     <t>03 EXTI - Limit switches</t>
   </si>
   <si>
@@ -298,12 +292,6 @@
     <t>EXTI1, rising/falling edge</t>
   </si>
   <si>
-    <t>YLE</t>
-  </si>
-  <si>
-    <t>YLE limit switch input</t>
-  </si>
-  <si>
     <t>PB2</t>
   </si>
   <si>
@@ -313,12 +301,6 @@
     <t>EXTI2, rising/falling edge</t>
   </si>
   <si>
-    <t>YRE</t>
-  </si>
-  <si>
-    <t>YRE limit switch input</t>
-  </si>
-  <si>
     <t>PB4 (NJTRST)</t>
   </si>
   <si>
@@ -328,9 +310,6 @@
     <t>EXTI4, rising/falling edge; physical pin also has NJTRST alternate debug name</t>
   </si>
   <si>
-    <t>YRI</t>
-  </si>
-  <si>
     <t>YRI limit switch input</t>
   </si>
   <si>
@@ -568,18 +547,6 @@
     <t>PG12</t>
   </si>
   <si>
-    <t>YLYB</t>
-  </si>
-  <si>
-    <t>YLEB</t>
-  </si>
-  <si>
-    <t>YREB</t>
-  </si>
-  <si>
-    <t>YRIB</t>
-  </si>
-  <si>
     <t>ZLI</t>
   </si>
   <si>
@@ -592,18 +559,6 @@
     <t>ZR Internal limit switch input</t>
   </si>
   <si>
-    <t>YLY Bottom limit switch input</t>
-  </si>
-  <si>
-    <t>YLE Bottom limit switch input</t>
-  </si>
-  <si>
-    <t>YRE Bottom limit switch input</t>
-  </si>
-  <si>
-    <t>YRI Bottom limit switch input</t>
-  </si>
-  <si>
     <t>GPIO_EXTI8</t>
   </si>
   <si>
@@ -655,16 +610,64 @@
     <t>EXTI0, rising/falling edge</t>
   </si>
   <si>
+    <t>EXTI9, rising/falling edge; physical pin also has NJTRST alternate debug name</t>
+  </si>
+  <si>
+    <t>EXTI10, rising/falling edge</t>
+  </si>
+  <si>
     <t>EXTI7, rising/falling edge</t>
   </si>
   <si>
     <t>EXTI8, rising/falling edge</t>
   </si>
   <si>
-    <t>EXTI10, rising/falling edge</t>
-  </si>
-  <si>
-    <t>EXTI9, rising/falling edge</t>
+    <t>PE7</t>
+  </si>
+  <si>
+    <t>XLI Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>XLIB</t>
+  </si>
+  <si>
+    <t>XLEB</t>
+  </si>
+  <si>
+    <t>XLE Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>XREB</t>
+  </si>
+  <si>
+    <t>XRE Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>XRIB</t>
+  </si>
+  <si>
+    <t>XRI Bottom limit switch input</t>
+  </si>
+  <si>
+    <t>XLI</t>
+  </si>
+  <si>
+    <t>XLI limit switch input</t>
+  </si>
+  <si>
+    <t>XLE</t>
+  </si>
+  <si>
+    <t>XLE limit switch input</t>
+  </si>
+  <si>
+    <t>XRE</t>
+  </si>
+  <si>
+    <t>XRE limit switch input</t>
+  </si>
+  <si>
+    <t>XRI</t>
   </si>
 </sst>
 </file>
@@ -1531,256 +1534,256 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>209</v>
+      </c>
+      <c r="B25" t="s">
+        <v>210</v>
+      </c>
+      <c r="C25" t="s">
         <v>86</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
         <v>87</v>
       </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
         <v>88</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>89</v>
-      </c>
-      <c r="E25" t="s">
-        <v>90</v>
-      </c>
-      <c r="F25" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>211</v>
+      </c>
+      <c r="B26" t="s">
+        <v>212</v>
+      </c>
+      <c r="C26" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
+      <c r="E26" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" t="s">
         <v>92</v>
-      </c>
-      <c r="B26" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" t="s">
-        <v>95</v>
-      </c>
-      <c r="F26" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>97</v>
+        <v>213</v>
       </c>
       <c r="B27" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>215</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E28" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E29" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D30" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>202</v>
+      </c>
+      <c r="B31" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" t="s">
         <v>182</v>
       </c>
-      <c r="B31" t="s">
-        <v>190</v>
-      </c>
-      <c r="C31" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" t="s">
-        <v>197</v>
-      </c>
       <c r="E31" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="F31" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D32" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="E32" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="F32" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B33" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D33" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="E33" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F33" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="B34" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="F34" t="s">
-        <v>213</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C35" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="E35" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="F35" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B36" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="C36" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D36" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E36" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="F36" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="C37" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="D37" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E37" t="s">
         <v>84</v>
@@ -1788,36 +1791,36 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="E38" t="s">
         <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B39" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E39" t="s">
         <v>79</v>
@@ -1828,16 +1831,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E40" t="s">
         <v>79</v>
@@ -1848,16 +1851,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B41" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E41" t="s">
         <v>79</v>
@@ -1868,16 +1871,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C42" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D42" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E42" t="s">
         <v>79</v>
@@ -1888,16 +1891,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B43" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D43" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="E43" t="s">
         <v>79</v>
@@ -1908,16 +1911,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B44" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D44" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="E44" t="s">
         <v>79</v>
@@ -1928,16 +1931,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B45" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D45" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E45" t="s">
         <v>79</v>
@@ -1948,16 +1951,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="B46" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="D46" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="E46" t="s">
         <v>79</v>
@@ -1968,36 +1971,36 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B47" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D47" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
         <v>79</v>
       </c>
       <c r="F47" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B48" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C48" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D48" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
         <v>79</v>
@@ -2008,16 +2011,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="C49" t="s">
+        <v>141</v>
+      </c>
+      <c r="D49" t="s">
         <v>148</v>
-      </c>
-      <c r="D49" t="s">
-        <v>155</v>
       </c>
       <c r="E49" t="s">
         <v>79</v>
@@ -2028,16 +2031,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="B50" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C50" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D50" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E50" t="s">
         <v>79</v>
@@ -2048,16 +2051,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B51" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="C51" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D51" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E51" t="s">
         <v>79</v>
@@ -2068,16 +2071,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B52" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C52" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D52" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E52" t="s">
         <v>79</v>
@@ -2088,16 +2091,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="B53" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D53" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E53" t="s">
         <v>79</v>
@@ -2108,16 +2111,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="B54" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D54" t="s">
         <v>164</v>
-      </c>
-      <c r="D54" t="s">
-        <v>171</v>
       </c>
       <c r="E54" t="s">
         <v>79</v>
@@ -2128,16 +2131,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B55" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D55" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E55" t="s">
         <v>79</v>
@@ -2148,16 +2151,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B56" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C56" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D56" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E56" t="s">
         <v>79</v>
@@ -2168,16 +2171,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="B57" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E57" t="s">
         <v>79</v>
